--- a/Test_Cases/05_Player/Ebook_Player_Test_Cases.xlsx
+++ b/Test_Cases/05_Player/Ebook_Player_Test_Cases.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
-    <col width="78" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="84" customWidth="1" min="8" max="8"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1032,8 +1032,884 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Verify e-book opens from Playlist e-book button</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>E-book is available in Playlist.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>E-book</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Playlist.
+2. Select e-book button.
+3. Observe player.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Whole e-book opens with chapter list and chapter resources panels.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>E-book remains open.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Verify book title and all chapters are displayed correctly</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Chapter list</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>UI / Functional</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>E-book open with multiple chapters.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>E-book</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1. Observe left chapter panel.
+2. Verify title and chapter numbering.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Book title and all chapters are displayed and correctly numbered.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Chapter list remains usable.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Verify first chapter is selected and highlighted by default</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Default chapter</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>E-book opened.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>E-book</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1. Open e-book.
+2. Observe chapter selection.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>First chapter opens by default and is highlighted.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>First chapter is active.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Verify chapter selection refreshes Chapter Resources</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Chapter switching</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>E-book has multiple chapters with different resources.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Two chapters</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1. Select chapter A.
+2. Observe resource list.
+3. Select chapter B.
+4. Observe resource list.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Resource list refreshes to match selected chapter.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Correct chapter resources are shown.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Verify chapter panel collapse and expand work</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Chapter panel</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>E-book open.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>E-book</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1. Collapse chapter panel.
+2. Observe arrow/state.
+3. Expand panel.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Panel collapses/reopens and toggle direction matches state.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Panel is in selected state.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Verify Chapter Resources count matches linked cards</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Resource count</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Chapter has linked resources.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Chapter with known resource count</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1. Select chapter.
+2. Count cards.
+3. Compare with displayed count.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Displayed count matches linked resource cards.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Resource list remains correct.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Verify resource, asset and quiz cards open from Chapter Resources</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nested resource types</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Chapter contains resource, asset and quiz cards.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Mixed chapter resources</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1. Select each card type.
+2. Observe nested player.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Each card opens in its appropriate player inside the e-book.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Nested player remains inside e-book.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Verify chapter with no resources displays expected empty state</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Empty chapter</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Chapter with no linked resources exists.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Empty chapter</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1. Select empty chapter.
+2. Observe right panel.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>No resources found! is displayed.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>E-book remains usable.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Verify resource panel scroll controls work at boundaries</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Resource scrolling</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Chapter has enough resources to scroll.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Many chapter resources</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1. Scroll up/down through resource list.
+2. Reach beginning and end.
+3. Observe controls.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Scroll controls move list correctly and are disabled at applicable ends.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Resource list remains usable.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Verify loading more resources occurs when scrolling to bottom</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Lazy resource loading</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Chapter has more resources than initial load.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Many resources</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1. Open chapter resources.
+2. Scroll to bottom.
+3. Observe list.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>More resources load when the bottom is reached where additional resources exist.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Additional resources are displayed.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Verify resource panel collapse and expand work</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Resource panel</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>E-book open.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>E-book</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1. Collapse resource panel.
+2. Observe.
+3. Expand panel.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Resource panel collapses/reopens correctly.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Panel is in selected state.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Verify nested worksheet/video/image/weblink/quiz open correctly</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nested players</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>E-book chapter contains supported nested resource types.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Mixed resources</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1. Open each listed nested type.
+2. Observe player.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Worksheet, video, image, weblink and quiz each open in the correct nested player.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Nested player remains within e-book.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Verify closing nested resource returns to e-book</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nested close</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Nested resource player open.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Nested resource</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1. Open nested resource.
+2. Close it.
+3. Observe e-book.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Nested resource closes and e-book remains open.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>E-book remains usable.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Verify e-book cannot open another e-book recursively</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Recursion boundary</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Nested player is open; an e-book resource is available if applicable.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>E-book resource</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1. Open resource from e-book.
+2. Attempt to open an e-book.
+3. Observe nesting.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>E-book does not recursively open another e-book inside nested player.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>E-book nesting remains one level deep.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Verify resource load failure shows error message inside e-book</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nested failure</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>A chapter resource can be made unavailable.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Failing resource</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1. Open failing resource from Chapter Resources.
+2. Observe content area.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Error while loading resource! is shown instead of a blank area.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>E-book remains usable.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Verify closing e-book returns to Whiteboard and closes nested content</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Book close</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>E-book and optionally nested resource are open.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>E-book</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1. Open e-book.
+2. Open nested resource.
+3. Close e-book.
+4. Observe Whiteboard.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>E-book closes, nested content closes, and user returns to Whiteboard.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Whiteboard is available.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1044,17 +1920,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1297,8 +2173,360 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Verify e-book opens from Playlist e-book button</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verify book title and all chapters are displayed correctly</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Verify first chapter is selected and highlighted by default</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Verify chapter selection refreshes Chapter Resources</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verify chapter panel collapse and expand work</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Verify Chapter Resources count matches linked cards</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Verify resource, asset and quiz cards open from Chapter Resources</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Verify chapter with no resources displays expected empty state</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Verify resource panel scroll controls work at boundaries</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Verify loading more resources occurs when scrolling to bottom</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Verify resource panel collapse and expand work</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Verify nested worksheet/video/image/weblink/quiz open correctly</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Verify closing nested resource returns to e-book</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Verify e-book cannot open another e-book recursively</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Verify resource load failure shows error message inside e-book</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC-EBOOK-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Verify closing e-book returns to Whiteboard and closes nested content</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:H26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>